--- a/config/xlsx/meridians.xlsx
+++ b/config/xlsx/meridians.xlsx
@@ -523,7 +523,7 @@
         <v>219</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
     </row>
@@ -541,7 +541,7 @@
         <v>219</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4" s="3" t="inlineStr"/>
     </row>
@@ -559,7 +559,7 @@
         <v>219</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3" t="inlineStr"/>
     </row>
@@ -577,7 +577,7 @@
         <v>219</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="3" t="inlineStr"/>
     </row>
@@ -595,7 +595,7 @@
         <v>219</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F7" s="3" t="inlineStr"/>
     </row>
@@ -613,7 +613,7 @@
         <v>219</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
     </row>
@@ -631,7 +631,7 @@
         <v>219</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" s="3" t="inlineStr"/>
     </row>
@@ -649,7 +649,7 @@
         <v>219</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" s="3" t="inlineStr"/>
     </row>
